--- a/data/combination-chart.xlsx
+++ b/data/combination-chart.xlsx
@@ -1,22 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\dashboardbuilder-v30\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="9190"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -24,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Month</t>
   </si>
@@ -69,16 +64,19 @@
   </si>
   <si>
     <t>Profit</t>
+  </si>
+  <si>
+    <t>Cost</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,9 +105,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -170,7 +171,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -205,7 +206,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -382,29 +383,35 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="4" max="4" width="5.90625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -419,7 +426,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -434,7 +441,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -449,7 +456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -464,7 +471,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -479,7 +486,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -494,7 +501,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -509,7 +516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -524,7 +531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -539,7 +546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -554,7 +561,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -569,7 +576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>12</v>
       </c>
